--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42600-2025 artfynd.xlsx
+++ b/artfynd/A 42600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128355175</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128354982</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128355228</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
